--- a/data/all_datasets/REDD/REDD_House6_stats/2026-03-31.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-03-31.xlsx
@@ -22913,7 +22913,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -23177,7 +23177,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E46" t="n">
